--- a/diseases/d092/1985-1989.xlsx
+++ b/diseases/d092/1985-1989.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17383,7 +17383,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22573,7 +22573,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23773,7 +23773,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">

--- a/diseases/d092/1985-1989.xlsx
+++ b/diseases/d092/1985-1989.xlsx
@@ -1013,7 +1013,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3413,7 +3413,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN25" t="b">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN29" t="b">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -7403,7 +7403,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8603,7 +8603,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9403,7 +9403,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9803,7 +9803,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -11393,7 +11393,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11793,7 +11793,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN63" t="b">
@@ -13393,7 +13393,7 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN65" t="b">
@@ -13793,7 +13793,7 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN67" t="b">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN69" t="b">
@@ -14593,7 +14593,7 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN71" t="b">
@@ -14993,7 +14993,7 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN73" t="b">
@@ -15393,7 +15393,7 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -16583,7 +16583,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -17383,7 +17383,7 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN85" t="b">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN89" t="b">
@@ -18583,7 +18583,7 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN91" t="b">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -19383,7 +19383,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -20183,7 +20183,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20583,7 +20583,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21773,7 +21773,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22573,7 +22573,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22973,7 +22973,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23773,7 +23773,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -24173,7 +24173,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24573,7 +24573,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24973,7 +24973,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -25773,7 +25773,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN129" t="b">
